--- a/docs/alliance-import-templates/01-合作企业导入模板-mock数据.xlsx
+++ b/docs/alliance-import-templates/01-合作企业导入模板-mock数据.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>填写说明：
 * 必填列。
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>周晓芳</t>
+  </si>
+  <si>
+    <t>产学研协同创新中心共建协议；智能装备制造专业群订单班培养协议</t>
+  </si>
+  <si>
+    <t>生物医药企业实践基地合作意向书；生物医药现代学徒制试点合作协议</t>
   </si>
 </sst>
 </file>
@@ -760,7 +766,7 @@
         <v>52</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>54</v>
@@ -804,7 +810,7 @@
         <v>63</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>65</v>

--- a/docs/alliance-import-templates/01-合作企业导入模板-mock数据.xlsx
+++ b/docs/alliance-import-templates/01-合作企业导入模板-mock数据.xlsx
@@ -10,14 +10,14 @@
     <sheet name="合作企业" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'合作企业'!$A$2:$N$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'合作企业'!$A$2:$R$2</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>填写说明：
 * 必填列。
@@ -26,7 +26,11 @@
 合作状态：洽谈中 / 合作中 / 已暂停 / 已终止（或 negotiating / active / paused / terminated），默认为 合作中
 合作评级：战略合作 / 深度合作 / 一般合作（或 strategic / deep / general），选填
 联系人 / 联系电话 / 联系邮箱 / 企业地址：选填
-【关联参考列】（青蓝色表头，导入时忽略）：关联项目 / 关联成果 / 关联协议 / 关联专家 为跨表单 mock 数据关联，多值用中文分号「；」分隔，需与对应导入模板中的名称保持一致</t>
+统一社会信用代码：文本，选填
+成立年份：四位数字，选填
+企业规模（人数）：数字，选填
+企业简介：文本，选填
+【关联参考列】（深蓝色表头，企业模板不导入）：关联项目 / 关联成果 / 关联协议 / 关联专家 为跨表单 mock 数据关联，多值用中文分号「；」分隔</t>
   </si>
   <si>
     <t>企业名称 *</t>
@@ -59,6 +63,18 @@
     <t>企业地址</t>
   </si>
   <si>
+    <t>统一社会信用代码</t>
+  </si>
+  <si>
+    <t>成立年份</t>
+  </si>
+  <si>
+    <t>企业规模（人数）</t>
+  </si>
+  <si>
+    <t>企业简介</t>
+  </si>
+  <si>
     <t>关联项目名称</t>
   </si>
   <si>
@@ -101,6 +117,18 @@
     <t>苏州市工业园区智能制造产业园1栋</t>
   </si>
   <si>
+    <t>91320594MA1P7ABC1X</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>专注工业机器人与视觉检测装备研发制造，拥有省级智能车间</t>
+  </si>
+  <si>
     <t>工业机器人视觉质检系统研发；工业互联网+智能制造协同创新中心</t>
   </si>
   <si>
@@ -140,6 +168,18 @@
     <t>南京市江宁区新能源汽车产业基地</t>
   </si>
   <si>
+    <t>91320115MA2KQ9XYZ5</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>新能源汽车电控系统研发与生产，服务多家主机厂</t>
+  </si>
+  <si>
     <t>新能源汽车电控系统实训基地建设</t>
   </si>
   <si>
@@ -179,13 +219,25 @@
     <t>无锡市滨湖区科教装备园</t>
   </si>
   <si>
+    <t>91320211MA1W6QEFG2</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>职业教育装备研发与产教融合服务提供商</t>
+  </si>
+  <si>
     <t>智能装备制造专业群人才共育；工业互联网+智能制造协同创新中心</t>
   </si>
   <si>
     <t>智能制造产教融合典型场景案例库</t>
   </si>
   <si>
-    <t>产学研协同创新中心共建协议</t>
+    <t>产学研协同创新中心共建协议；智能装备制造专业群订单班培养协议</t>
   </si>
   <si>
     <t>陈晓东</t>
@@ -212,29 +264,35 @@
     <t>常州市新北区生物医药产业园</t>
   </si>
   <si>
+    <t>91320411MA1Y2BXYZ3</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>生物医药研发与生产，覆盖原料药与制剂一体化布局</t>
+  </si>
+  <si>
     <t>生物医药现代学徒制试点</t>
   </si>
   <si>
     <t>生物医药校企协同育人调研报告</t>
   </si>
   <si>
-    <t>生物医药企业实践基地合作意向书</t>
+    <t>生物医药企业实践基地合作意向书；生物医药现代学徒制试点合作协议</t>
   </si>
   <si>
     <t>周晓芳</t>
-  </si>
-  <si>
-    <t>产学研协同创新中心共建协议；智能装备制造专业群订单班培养协议</t>
-  </si>
-  <si>
-    <t>生物医药企业实践基地合作意向书；生物医药现代学徒制试点合作协议</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -251,13 +309,8 @@
       <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
-    <font>
-      <family val="2"/>
-      <color rgb="FF2E74B5"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -267,6 +320,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E74B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -292,10 +350,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -574,27 +632,36 @@
     <col customWidth="true" max="6" min="5" width="22"/>
     <col customWidth="true" max="8" min="7" width="18"/>
     <col customWidth="true" max="9" min="9" width="24"/>
-    <col customWidth="true" max="13" min="10" width="36"/>
-    <col customWidth="true" max="14" min="14" width="24"/>
+    <col customWidth="true" max="10" min="10" width="36"/>
+    <col customWidth="true" max="11" min="11" width="28"/>
+    <col customWidth="true" max="12" min="12" width="14"/>
+    <col customWidth="true" max="13" min="13" width="18"/>
+    <col customWidth="true" max="14" min="14" width="48"/>
+    <col customWidth="true" max="17" min="15" width="36"/>
+    <col customWidth="true" max="18" min="18" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="210" customHeight="true">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="240" customHeight="true">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" ht="26" customHeight="true">
       <c r="A2" s="1" t="s">
@@ -627,199 +694,259 @@
       <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="true">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="3" t="s">
         <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="true">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="true">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" t="s">
         <v>66</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>54</v>
+      <c r="O5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="true">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
+      </c>
+      <c r="K6" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$N$2"/>
+  <autoFilter ref="$A$2:$R$2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
 </worksheet>
 </file>